--- a/test/fixtures/hardcoded.xlsx
+++ b/test/fixtures/hardcoded.xlsx
@@ -419,6 +419,7 @@
       </c>
       <c r="C2">
         <f>VLOOKUP(A2,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -430,6 +431,7 @@
       </c>
       <c r="C3">
         <f>VLOOKUP(A3,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -441,6 +443,7 @@
       </c>
       <c r="C4">
         <f>VLOOKUP(A4,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -452,6 +455,7 @@
       </c>
       <c r="C5">
         <f>VLOOKUP(A5,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -463,6 +467,7 @@
       </c>
       <c r="C6">
         <f>VLOOKUP(A6,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -474,6 +479,7 @@
       </c>
       <c r="C7">
         <f>VLOOKUP(A7,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -485,6 +491,7 @@
       </c>
       <c r="C8">
         <f>VLOOKUP(A8,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -496,6 +503,7 @@
       </c>
       <c r="C9">
         <f>VLOOKUP(A9,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -507,6 +515,7 @@
       </c>
       <c r="C10">
         <f>VLOOKUP(A10,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -518,6 +527,7 @@
       </c>
       <c r="C11">
         <f>VLOOKUP(A11,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -529,6 +539,7 @@
       </c>
       <c r="C12">
         <f>VLOOKUP(A12,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -540,6 +551,7 @@
       </c>
       <c r="C13">
         <f>VLOOKUP(A13,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -551,6 +563,7 @@
       </c>
       <c r="C14">
         <f>VLOOKUP(A14,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -562,6 +575,7 @@
       </c>
       <c r="C15">
         <f>VLOOKUP(A15,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -573,6 +587,7 @@
       </c>
       <c r="C16">
         <f>VLOOKUP(A16,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -584,6 +599,7 @@
       </c>
       <c r="C17">
         <f>VLOOKUP(A17,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -595,6 +611,7 @@
       </c>
       <c r="C18">
         <f>VLOOKUP(A18,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -606,6 +623,7 @@
       </c>
       <c r="C19">
         <f>VLOOKUP(A19,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -617,6 +635,7 @@
       </c>
       <c r="C20">
         <f>VLOOKUP(A20,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -628,6 +647,7 @@
       </c>
       <c r="C21">
         <f>VLOOKUP(A21,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -639,6 +659,7 @@
       </c>
       <c r="C22">
         <f>VLOOKUP(A22,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -650,6 +671,7 @@
       </c>
       <c r="C23">
         <f>VLOOKUP(A23,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -661,6 +683,7 @@
       </c>
       <c r="C24">
         <f>VLOOKUP(A24,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -672,6 +695,7 @@
       </c>
       <c r="C25">
         <f>VLOOKUP(A25,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -683,6 +707,7 @@
       </c>
       <c r="C26">
         <f>VLOOKUP(A26,$A$2:$B$26,2,FALSE)*1.2</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
